--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NORTH_CAROLINA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NORTH_CAROLINA_2019.xlsx
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C169">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C296">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C701">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C823">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C868">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C877">
